--- a/db/pns-scrna.xlsx
+++ b/db/pns-scrna.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cell_types" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cell_subtypes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="processing" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="markers" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +48,13 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +74,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -122,6 +134,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -240,12 +255,12 @@
     <author>小玖</author>
   </authors>
   <commentList>
-    <comment ref="I2" authorId="0" shapeId="0">
+    <comment ref="J2" authorId="0" shapeId="0">
       <text>
         <t>原文未给各细胞大类的绝对数/精确占比(仅 Fig.1A 比例图)；总数 keloid 47,478 + normal skin 19,598。故各类 n_cells_or_pct=NA</t>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
+    <comment ref="L2" authorId="0" shapeId="0">
       <text>
         <t>marker 列表源 Supplementary Table 2(marker genes information)；细胞类型经 Fig.1A UMAP + clustermarker 鉴定</t>
       </text>
@@ -255,7 +270,7 @@
         <t>scRNA 共识别 6 个施万亚型：SC-Skin/SC-Promyel/SC-Keloid/SC-Prolif/SC-EC/SC-FB(Fig.3)；keloid 主体=SC-Keloid(去分化/促纤维,NES;IGFBP3;IGFBP5;TGFBI;TNFAIP6+)</t>
       </text>
     </comment>
-    <comment ref="K10" authorId="0" shapeId="0">
+    <comment ref="L10" authorId="0" shapeId="0">
       <text>
         <t>marker S100B;NGFR 源 Table S2；蛋白验证 S100B/NGFR/SOX10/Nestin/JUN(Fig.4)、抗体 Table S3；亚型分析 Fig.3</t>
       </text>
@@ -2497,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2549,22 +2564,27 @@
           <t>markers</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>mark_status</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>n_cells_or_pct</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>annotation_method</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
@@ -2606,22 +2626,27 @@
           <t>PDGFRA;LUM;COL1A1;DCN;FBLN1</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -2663,22 +2688,27 @@
           <t>ACTA2;RGS5</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -2720,22 +2750,27 @@
           <t>KRT10;KRT1;KRT14;KRT5</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -2777,22 +2812,27 @@
           <t>SELE;VWF</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -2834,22 +2874,27 @@
           <t>VWF;LYVE1</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -2891,22 +2936,27 @@
           <t>CD3D;CD2;CXCR4</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -2948,22 +2998,27 @@
           <t>CD68;AIF1</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A;Fig.9</t>
         </is>
@@ -3005,22 +3060,27 @@
           <t>AIF1;FCER1A</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -3062,22 +3122,27 @@
           <t>S100B;NGFR</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>Table S2;Table S3;Fig.1A;Fig.3;Fig.4</t>
         </is>
@@ -3119,22 +3184,27 @@
           <t>PMEL;MLANA</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -3176,22 +3246,27 @@
           <t>HBB;HBA1</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Table S2;Fig.1A</t>
         </is>
@@ -3235,20 +3310,25 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
         </is>
@@ -3292,20 +3372,25 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
         </is>
@@ -3349,20 +3434,25 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D;Fig.4A</t>
         </is>
@@ -3406,20 +3496,25 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
         </is>
@@ -3463,20 +3558,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
         </is>
@@ -3520,20 +3620,25 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E;Fig.4A</t>
         </is>
@@ -3577,20 +3682,25 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
         </is>
@@ -3634,20 +3744,25 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
         </is>
@@ -3691,20 +3806,25 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D</t>
         </is>
@@ -3748,20 +3868,25 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E</t>
         </is>
@@ -3805,20 +3930,25 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E</t>
         </is>
@@ -3862,20 +3992,25 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>rat</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>manual-marker</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
         </is>
@@ -4915,4 +5050,4618 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>marker_id</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>ct_id</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>subtype_id</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>gene_symbol</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>original_symbol</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>evidence_level</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>source_section</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>source_context</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M00001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>S00001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MBP</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MBP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Skin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M00002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S00001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PLP1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PLP1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Skin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M00003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S00001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PMP22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PMP22</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Skin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>M00004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S00001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MPZ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MPZ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Skin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>M00005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S00001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NCAM1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NCAM1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Skin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>M00006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>S00001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L1CAM</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L1CAM</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Skin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M00007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S00001</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SCN7A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SCN7A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Skin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M00008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>S00002</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>POU3F1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>POU3F1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Promyel）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>M00009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>S00002</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GFAP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GFAP</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Promyel）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>M00010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>S00002</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FOXO4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FOXO4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Promyel）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M00011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>S00003</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NES</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NES</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.3D;Fig.4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Keloid）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>M00012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>S00003</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IGFBP3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IGFBP3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.3D;Fig.4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Keloid）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M00013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>S00003</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IGFBP5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IGFBP5</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.3D;Fig.4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Keloid）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M00014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>S00003</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TGFBI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TGFBI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.3D;Fig.4</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Keloid）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>M00015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>S00003</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TNFAIP6</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TNFAIP6</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.3D;Fig.4</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Keloid）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M00016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>S00004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MKI67</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MKI67</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3D;Fig.5B</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Prolif）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M00017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>S00004</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TOP2A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TOP2A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3D;Fig.5B</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-Prolif）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>M00018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>S00005</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SELE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SELE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5C</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-EC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>M00019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>S00005</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ICAM1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ICAM1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5C</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-EC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>M00020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>S00006</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LUM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LUM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5D</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-FB）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>M00021</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>S00006</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DCN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DCN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5D</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-FB）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>M00022</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>S00006</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>THY1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>THY1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3C;Fig.5D</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0006, subtype=Schwann cell/SC-FB）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M00023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>S00007</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mbp</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Mbp</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/myelinating）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M00024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>S00007</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pmp22</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pmp22</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/myelinating）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M00025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>S00007</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Plp1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Plp1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/myelinating）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M00026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>S00007</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pou3f1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Pou3f1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/myelinating）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>M00027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>S00007</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Egr2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Egr2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/myelinating）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>M00028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>S00008</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ngfr</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ngfr</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/non-myelinating/Remak）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>M00029</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>S00008</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cdh2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Cdh2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/non-myelinating/Remak）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>M00030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>S00008</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>L1cam</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>L1cam</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/non-myelinating/Remak）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>M00031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>S00008</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ednrb</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ednrb</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/non-myelinating/Remak）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>M00032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>S00009</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ngfr</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ngfr</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3D;Results/Schwann cells</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/repair）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>M00033</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>S00009</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sox10</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sox10</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3D;Results/Schwann cells</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/repair）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>M00034</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>S00009</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Gdnf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Gdnf</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3D;Results/Schwann cells</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/repair）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>M00035</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>S00009</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bdnf</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bdnf</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3D;Results/Schwann cells</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/repair）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>M00036</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>S00009</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Artn</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Artn</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fig.3A;Fig.3D;Results/Schwann cells</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/repair）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>M00037</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>S00010</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mki67</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mki67</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fig.3A;Results/Computational analysis of scRNA-seq data</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/proliferating）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>M00038</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>S00010</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Top2a</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Top2a</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fig.3A;Results/Computational analysis of scRNA-seq data</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>从 cell_subtypes 迁移（paper=P0007, subtype=Schwann cell/proliferating）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>M00039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>C00065</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>M00040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>C00065</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LUM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LUM</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>M00041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>C00065</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>COL1A1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>COL1A1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>M00042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>C00065</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DCN</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DCN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>M00043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C00065</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FBLN1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FBLN1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>M00044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>C00066</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ACTA2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ACTA2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Pericyte/SMC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>M00045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>C00066</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RGS5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RGS5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Pericyte/SMC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>M00046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C00067</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>KRT10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>KRT10</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Keratinocyte(uncontrolled)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>M00047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C00067</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>KRT1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>KRT1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Keratinocyte(uncontrolled)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>M00048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>C00067</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>KRT14</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>KRT14</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Keratinocyte(uncontrolled)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>M00049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>C00067</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KRT5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>KRT5</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Keratinocyte(uncontrolled)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>M00050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>C00068</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SELE</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SELE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Endothelial）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>M00051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>C00068</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VWF</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>VWF</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Endothelial）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>M00052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>C00069</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VWF</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>VWF</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Endothelial）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>M00053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>C00069</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LYVE1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LYVE1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Endothelial）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>M00054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C00070</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CD3D</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CD3D</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>M00055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C00070</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CD2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CD2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>M00056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>C00070</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CXCR4</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CXCR4</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>M00057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>C00071</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CD68</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CD68</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A;Fig.9</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>M00058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>C00071</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AIF1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AIF1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A;Fig.9</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>M00059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>C00072</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AIF1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AIF1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>M00060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>C00072</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FCER1A</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FCER1A</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>M00061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>C00073</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S100B</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>S100B</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Table S2;Table S3;Fig.1A;Fig.3;Fig.4</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>M00062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>C00073</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NGFR</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NGFR</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Table S2;Table S3;Fig.1A;Fig.3;Fig.4</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>M00063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>C00074</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PMEL</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PMEL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Melanocyte(uncontrolled)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>M00064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>C00074</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MLANA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>MLANA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Melanocyte(uncontrolled)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>M00065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>C00075</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HBB</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>HBB</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Erythrocyte）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>M00066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>C00075</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HBA1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>HBA1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Table S2;Fig.1A</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0006, cell_type=Erythrocyte）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>M00067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>C00076</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mbp</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Mbp</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>M00068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>C00076</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pmp22</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Pmp22</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>M00069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>C00076</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plp1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Plp1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>M00070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>C00076</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pou3f1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Pou3f1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>M00071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>C00076</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Egr2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Egr2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>M00072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>C00077</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ngfr</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ngfr</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>M00073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>C00077</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>P75ntr</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>P75ntr</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>M00074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>C00077</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Cdh2</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Cdh2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>M00075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C00077</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>L1cam</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>L1cam</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>M00076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>C00077</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ednrb</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ednrb</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>M00077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>C00077</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Emp1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Emp1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>M00078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>C00077</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sema3e</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sema3e</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.2C</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=Schwann cell）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>M00079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>C00078</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>M00080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>C00078</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Etv1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Etv1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>M00081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>C00078</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wif1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Wif1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>M00082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>C00078</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sox9</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Sox9</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>M00083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>C00078</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Osr2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Osr2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>M00084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>C00078</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Meox1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Meox1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>M00085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>C00079</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>M00086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>C00079</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pcolce2</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Pcolce2</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>M00087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>C00079</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Dpp4</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Dpp4</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>M00088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>C00079</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Dpt</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Dpt</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>M00089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>C00080</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>M00090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>C00080</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Slc2a1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Slc2a1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>M00091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>C00080</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Casq2</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Casq2</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>M00092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>C00080</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Msln</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Msln</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>M00093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>C00081</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Pdgfra</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>M00094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>C00081</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Dlk1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Dlk1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>M00095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>C00081</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Mest</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Mest</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E;Fig.4A</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=fibroblast）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>M00096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>C00082</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pecam1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Pecam1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=endothelial）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>M00097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>C00082</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Plvap</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Plvap</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=endothelial）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>M00098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>C00082</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Esam</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=endothelial）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>M00099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>C00083</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Desmin</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Desmin</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=pericyte/SMC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>M00100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>C00083</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Mylk</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Mylk</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=pericyte/SMC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>M00101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>C00083</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Acta2</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Acta2</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=pericyte/SMC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>M00102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>C00083</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Rgs5</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Rgs5</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=pericyte/SMC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>M00103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>C00084</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Aif1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aif1</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>M00104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>C00084</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Cd68</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Cd68</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1D</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>M00105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>C00085</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Ptprcap</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Ptprcap</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>M00106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>C00085</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Trbc2</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Trbc2</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>M00107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>C00086</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Cd19</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Cd19</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>M00108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>C00087</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Cpa3</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Cpa3</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>imported</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Results/Cell types were defined based on the expression of established marker genes;Fig.1C;Fig.1E</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>从 cell_types 迁移（paper=P0007, cell_type=macrophage/immune）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>